--- a/data/trans_orig/P25C_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dejó de fumar con o sin ayuda específica en 2023</t>
+          <t>Población según si dejó de fumar con o sin ayuda específica en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3725</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43250</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>55917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36430</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80288</t>
+          <t>82167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97565</t>
+          <t>98967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54890</t>
+          <t>55369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62817</t>
+          <t>63006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139534</t>
+          <t>140425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>159230</t>
+          <t>158545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60601</t>
+          <t>61049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>41647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47756</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105089</t>
+          <t>104593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114643</t>
+          <t>114430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85433</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93228</t>
+          <t>93432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51336</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56741</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140400</t>
+          <t>140548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149011</t>
+          <t>149143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>377</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44533</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50670</t>
+          <t>50923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>55695</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111102</t>
+          <t>111716</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119695</t>
+          <t>120013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77820</t>
+          <t>77295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>87786</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192469</t>
+          <t>192813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>206016</t>
+          <t>206042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>310108</t>
+          <t>310249</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>344531</t>
+          <t>344810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>344897</t>
+          <t>345410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>381772</t>
+          <t>382421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>68636</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>37539</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97483</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>782085</t>
+          <t>780917</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>831587</t>
+          <t>834511</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>299448</t>
+          <t>299904</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>316454</t>
+          <t>316421</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1089513</t>
+          <t>1089264</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1150053</t>
+          <t>1149535</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43469</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58831</t>
+          <t>62116</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28347</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17419</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35539</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90535</t>
+          <t>95504</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82167</t>
+          <t>86054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98967</t>
+          <t>103309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55369</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>150374</t>
+          <t>156644</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140425</t>
+          <t>145488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158545</t>
+          <t>165485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>185348</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>185348</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>185348</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65879</t>
+          <t>64931</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>66818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41647</t>
+          <t>41315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>47870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111158</t>
+          <t>110292</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>104800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114430</t>
+          <t>113890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91003</t>
+          <t>103245</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85559</t>
+          <t>98297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93432</t>
+          <t>105873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54955</t>
+          <t>61666</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51226</t>
+          <t>57845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56812</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>145956</t>
+          <t>164911</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140548</t>
+          <t>158844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149143</t>
+          <t>168397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42899</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>43628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>53923</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50923</t>
+          <t>50301</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>55104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>116895</t>
+          <t>136740</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111716</t>
+          <t>130774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120013</t>
+          <t>140251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>83463</t>
+          <t>94690</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77295</t>
+          <t>87672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87786</t>
+          <t>99344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>200358</t>
+          <t>231430</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192813</t>
+          <t>223427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>206042</t>
+          <t>237620</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>142359</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>142359</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>142359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>216648</t>
+          <t>249767</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>216648</t>
+          <t>249767</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>216648</t>
+          <t>249767</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>337101</t>
+          <t>103461</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>310249</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>344810</t>
+          <t>107493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>42406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>371412</t>
+          <t>143517</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>345410</t>
+          <t>135919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382421</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>113542</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>113542</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>113542</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>157783</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>157783</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>157783</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68636</t>
+          <t>64357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>72222</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>64444</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97732</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>805868</t>
+          <t>611308</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>780917</t>
+          <t>595862</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>834511</t>
+          <t>622759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>308907</t>
+          <t>335291</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>299904</t>
+          <t>326142</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>316421</t>
+          <t>343208</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1114774</t>
+          <t>946599</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1089264</t>
+          <t>929283</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1149535</t>
+          <t>961665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
